--- a/data/20250725_所有外卖订单.xlsx
+++ b/data/20250725_所有外卖订单.xlsx
@@ -189,7 +189,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS14"/>
+  <dimension ref="A1:AS16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -669,12 +669,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>W1202507251549474067</t>
+          <t>W1202507251600194423</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>W1202507251549474066S</t>
+          <t>W1202507251600194422S</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25 15:49:47</t>
+          <t>2025-07-25 16:00:19</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25 15:49:47</t>
+          <t>2025-07-25 16:00:19</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -739,17 +739,17 @@
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25 23:55:00</t>
+          <t>2025-07-26 23:55:00</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>2025-07-26 00:00:00-23:59:59</t>
+          <t>2025-07-27 00:00:00-23:59:59</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>10279</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>W1202507251549414065</t>
+          <t>W1202507251600104416</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>W1202507251549414064S</t>
+          <t>W1202507251600104415S</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25 15:49:41</t>
+          <t>2025-07-25 16:00:10</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25 15:49:41</t>
+          <t>2025-07-25 16:00:10</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -966,17 +966,17 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25 23:55:00</t>
+          <t>2025-07-26 23:55:00</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2025-07-26 00:00:00-23:59:59</t>
+          <t>2025-07-27 00:00:00-23:59:59</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10276</t>
+          <t>10278</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -1123,27 +1123,27 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>W1202507251517543521</t>
+          <t>W1202507251549474067</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>W1202507251517543520S</t>
+          <t>W1202507251549474066S</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>210512155434479008317</t>
+          <t>20230703101319100507792</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13861905166</t>
+          <t>17826157137</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>邱枫</t>
+          <t>于池</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -1153,17 +1153,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>政企客户部</t>
+          <t>数智化支撑中心</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25 15:17:54</t>
+          <t>2025-07-25 15:49:47</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25 15:17:54</t>
+          <t>2025-07-25 15:49:47</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>西点</t>
+          <t>咖啡测试 请勿点击</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1193,17 +1193,17 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2025-07-30 23:55:00</t>
+          <t>2025-07-25 23:55:00</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2025-07-31 00:00:00-23:59:59</t>
+          <t>2025-07-26 00:00:00-23:59:59</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>10277</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>123050622534</t>
+          <t>125072239625</t>
         </is>
       </c>
       <c r="AN5" s="2" t="inlineStr">
         <is>
-          <t>芋泥雪贝</t>
+          <t>冰美式</t>
         </is>
       </c>
       <c r="AO5" s="2" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="AP5" s="2" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AQ5" s="2" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AR5" s="2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="AS5" s="2" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -1350,27 +1350,27 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>W1202507251517323511</t>
+          <t>W1202507251549414065</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>W1202507251517323510S</t>
+          <t>W1202507251549414064S</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>210512155434479008317</t>
+          <t>20230703101319100507792</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13861905166</t>
+          <t>17826157137</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>邱枫</t>
+          <t>于池</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1380,17 +1380,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>政企客户部</t>
+          <t>数智化支撑中心</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25 15:17:32</t>
+          <t>2025-07-25 15:49:41</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25 15:17:32</t>
+          <t>2025-07-25 15:49:41</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>西点</t>
+          <t>咖啡测试 请勿点击</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1420,17 +1420,17 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2025-07-29 23:55:00</t>
+          <t>2025-07-25 23:55:00</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2025-07-30 00:00:00-23:59:59</t>
+          <t>2025-07-26 00:00:00-23:59:59</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>10274</t>
+          <t>10276</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1460,7 +1460,7 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
@@ -1520,37 +1520,37 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>125072578406</t>
+          <t>125072239625</t>
         </is>
       </c>
       <c r="AN6" s="2" t="inlineStr">
         <is>
-          <t>雪芙紫薯面包</t>
+          <t>冰美式</t>
         </is>
       </c>
       <c r="AO6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AP6" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AQ6" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AR6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AP6" s="2" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="AQ6" s="2" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="AR6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AS6" s="2" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>0.0</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>W1202507251516493498</t>
+          <t>W1202507251517543521</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>W1202507251516493497S</t>
+          <t>W1202507251517543520S</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25 15:16:49</t>
+          <t>2025-07-25 15:17:54</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25 15:16:49</t>
+          <t>2025-07-25 15:17:54</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>外卖,西点</t>
+          <t>西点</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1647,17 +1647,17 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 23:55:00</t>
+          <t>2025-07-30 23:55:00</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2025-07-29 00:00:00-23:59:59</t>
+          <t>2025-07-31 00:00:00-23:59:59</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>10273</t>
+          <t>10275</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>41.00</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>41.00</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
@@ -1747,12 +1747,12 @@
       </c>
       <c r="AM7" s="2" t="inlineStr">
         <is>
-          <t>0000183043</t>
+          <t>123050622534</t>
         </is>
       </c>
       <c r="AN7" s="2" t="inlineStr">
         <is>
-          <t>虎皮蛋糕</t>
+          <t>芋泥雪贝</t>
         </is>
       </c>
       <c r="AO7" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="AP7" s="2" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="AQ7" s="2" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="AR7" s="2" t="inlineStr">
@@ -1777,154 +1777,154 @@
       </c>
       <c r="AS7" s="2" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>8.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>666210500150927</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>南通生产调度中心</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>118509</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>南通生产调度中心</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>W1202507251517323511</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>W1202507251517323510S</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>210512155434479008317</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>13861905166</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>邱枫</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>南通分公司</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>政企客户部</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-07-25 15:17:32</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-07-25 15:17:32</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>在线购物</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>西点</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>在线付款</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>自提</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>备货中</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-07-29 23:55:00</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-07-30 00:00:00-23:59:59</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>10274</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>7.00</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>7.00</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="AD8" s="2" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="AE8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>未打印</t>
         </is>
       </c>
       <c r="AF8" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="AJ8" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>食堂</t>
         </is>
       </c>
       <c r="AK8" s="2" t="inlineStr">
@@ -1974,12 +1974,12 @@
       </c>
       <c r="AM8" s="2" t="inlineStr">
         <is>
-          <t>0000201505</t>
+          <t>125072578406</t>
         </is>
       </c>
       <c r="AN8" s="2" t="inlineStr">
         <is>
-          <t>盐水鸭边腿</t>
+          <t>雪芙紫薯面包</t>
         </is>
       </c>
       <c r="AO8" s="2" t="inlineStr">
@@ -1989,12 +1989,12 @@
       </c>
       <c r="AP8" s="2" t="inlineStr">
         <is>
-          <t>35.00</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="AQ8" s="2" t="inlineStr">
         <is>
-          <t>35.00</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="AR8" s="2" t="inlineStr">
@@ -2004,7 +2004,7 @@
       </c>
       <c r="AS8" s="2" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>7.0</t>
         </is>
       </c>
     </row>
@@ -2031,27 +2031,27 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>W1202507251501103144</t>
+          <t>W1202507251516493498</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>W1202507251501103143S</t>
+          <t>W1202507251516493497S</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>210512155433477968766</t>
+          <t>210512155434479008317</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13912260468</t>
+          <t>13861905166</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>曹春燕</t>
+          <t>邱枫</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>品质管理部</t>
+          <t>政企客户部</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25 15:01:10</t>
+          <t>2025-07-25 15:16:49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25 15:01:10</t>
+          <t>2025-07-25 15:16:49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>西点</t>
+          <t>外卖,西点</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -2101,17 +2101,17 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2025-07-29 23:55:00</t>
+          <t>2025-07-28 23:55:00</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2025-07-30 00:00:00-23:59:59</t>
+          <t>2025-07-29 00:00:00-23:59:59</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>10272</t>
+          <t>10273</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>41.00</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>41.00</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="AM9" s="2" t="inlineStr">
         <is>
-          <t>125072578406</t>
+          <t>0000183043</t>
         </is>
       </c>
       <c r="AN9" s="2" t="inlineStr">
         <is>
-          <t>雪芙紫薯面包</t>
+          <t>虎皮蛋糕</t>
         </is>
       </c>
       <c r="AO9" s="2" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="AP9" s="2" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="AQ9" s="2" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="AR9" s="2" t="inlineStr">
@@ -2231,154 +2231,154 @@
       </c>
       <c r="AS9" s="2" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>6.0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>666210500150927</t>
+          <t/>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>南通生产调度中心</t>
+          <t/>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>118509</t>
+          <t/>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>南通生产调度中心</t>
+          <t/>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>W1202507251500433139</t>
+          <t/>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>W1202507251500433138S</t>
+          <t/>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>210512155433477968766</t>
+          <t/>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13912260468</t>
+          <t/>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>曹春燕</t>
+          <t/>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>南通分公司</t>
+          <t/>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>品质管理部</t>
+          <t/>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25 15:00:43</t>
+          <t/>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25 15:00:43</t>
+          <t/>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>在线购物</t>
+          <t/>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>面点,西点</t>
+          <t/>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>在线付款</t>
+          <t/>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>自提</t>
+          <t/>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>备货中</t>
+          <t/>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2025-07-28 23:55:00</t>
+          <t/>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2025-07-29 00:00:00-23:59:59</t>
+          <t/>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10271</t>
+          <t/>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>26.00</t>
+          <t/>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>26.00</t>
+          <t/>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="AE10" s="2" t="inlineStr">
         <is>
-          <t>未打印</t>
+          <t/>
         </is>
       </c>
       <c r="AF10" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="AJ10" s="2" t="inlineStr">
         <is>
-          <t>食堂</t>
+          <t/>
         </is>
       </c>
       <c r="AK10" s="2" t="inlineStr">
@@ -2428,27 +2428,27 @@
       </c>
       <c r="AM10" s="2" t="inlineStr">
         <is>
-          <t>0000183535</t>
+          <t>0000201505</t>
         </is>
       </c>
       <c r="AN10" s="2" t="inlineStr">
         <is>
-          <t>三丁包</t>
+          <t>盐水鸭边腿</t>
         </is>
       </c>
       <c r="AO10" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AP10" s="2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="AQ10" s="2" t="inlineStr">
         <is>
-          <t>20.00</t>
+          <t>35.00</t>
         </is>
       </c>
       <c r="AR10" s="2" t="inlineStr">
@@ -2458,154 +2458,154 @@
       </c>
       <c r="AS10" s="2" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>35.0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>666210500150927</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>南通生产调度中心</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>118509</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>南通生产调度中心</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>W1202507251501103144</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>W1202507251501103143S</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>210512155433477968766</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>13912260468</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>曹春燕</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>南通分公司</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>品质管理部</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-07-25 15:01:10</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-07-25 15:01:10</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>在线购物</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>西点</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>在线付款</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>自提</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>备货中</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-07-29 23:55:00</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>2025-07-30 00:00:00-23:59:59</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>10272</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>7.00</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>7.00</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>0</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AE11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>未打印</t>
         </is>
       </c>
       <c r="AF11" s="2" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="AJ11" s="2" t="inlineStr">
         <is>
-          <t/>
+          <t>食堂</t>
         </is>
       </c>
       <c r="AK11" s="2" t="inlineStr">
@@ -2655,12 +2655,12 @@
       </c>
       <c r="AM11" s="2" t="inlineStr">
         <is>
-          <t>0000183042</t>
+          <t>125072578406</t>
         </is>
       </c>
       <c r="AN11" s="2" t="inlineStr">
         <is>
-          <t>热狗面包</t>
+          <t>雪芙紫薯面包</t>
         </is>
       </c>
       <c r="AO11" s="2" t="inlineStr">
@@ -2670,12 +2670,12 @@
       </c>
       <c r="AP11" s="2" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="AQ11" s="2" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="AR11" s="2" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="AS11" s="2" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>7.0</t>
         </is>
       </c>
     </row>
@@ -2712,27 +2712,27 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>W1202507251130579419</t>
+          <t>W1202507251500433139</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>W1202507251130579418S</t>
+          <t>W1202507251500433138S</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>20230703101319100507792</t>
+          <t>210512155433477968766</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17826157137</t>
+          <t>13912260468</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>于池</t>
+          <t>曹春燕</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -2742,17 +2742,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>数智化支撑中心</t>
+          <t>品质管理部</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25 11:30:57</t>
+          <t>2025-07-25 15:00:43</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25 11:30:57</t>
+          <t>2025-07-25 15:00:43</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -2762,7 +2762,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>咖啡测试 请勿点击</t>
+          <t>面点,西点</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -2782,17 +2782,17 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25 23:55:00</t>
+          <t>2025-07-28 23:55:00</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2025-07-26 00:00:00-23:59:59</t>
+          <t>2025-07-29 00:00:00-23:59:59</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>10270</t>
+          <t>10271</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>26.00</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>26.00</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
@@ -2882,184 +2882,184 @@
       </c>
       <c r="AM12" s="2" t="inlineStr">
         <is>
-          <t>125072239625</t>
+          <t>0000183535</t>
         </is>
       </c>
       <c r="AN12" s="2" t="inlineStr">
         <is>
-          <t>冰美式</t>
+          <t>三丁包</t>
         </is>
       </c>
       <c r="AO12" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AP12" s="2" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="AQ12" s="2" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="AR12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AP12" s="2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AQ12" s="2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AR12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AS12" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>20.0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>666210500150927</t>
+          <t/>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>南通生产调度中心</t>
+          <t/>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>118509</t>
+          <t/>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>南通生产调度中心</t>
+          <t/>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>W1202507251124009271</t>
+          <t/>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>W1202507251124009270S</t>
+          <t/>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20230703101319100507792</t>
+          <t/>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17826157137</t>
+          <t/>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>于池</t>
+          <t/>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>南通分公司</t>
+          <t/>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>数智化支撑中心</t>
+          <t/>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25 11:24:00</t>
+          <t/>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25 11:24:00</t>
+          <t/>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>在线购物</t>
+          <t/>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>咖啡测试 请勿点击</t>
+          <t/>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>在线付款</t>
+          <t/>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>自提</t>
+          <t/>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>备货中</t>
+          <t/>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2025-07-25 23:55:00</t>
+          <t/>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2025-07-26 00:00:00-23:59:59</t>
+          <t/>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t/>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t/>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t/>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="AE13" s="2" t="inlineStr">
         <is>
-          <t>未打印</t>
+          <t/>
         </is>
       </c>
       <c r="AF13" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="AJ13" s="2" t="inlineStr">
         <is>
-          <t>食堂</t>
+          <t/>
         </is>
       </c>
       <c r="AK13" s="2" t="inlineStr">
@@ -3109,12 +3109,12 @@
       </c>
       <c r="AM13" s="2" t="inlineStr">
         <is>
-          <t>125072239625</t>
+          <t>0000183042</t>
         </is>
       </c>
       <c r="AN13" s="2" t="inlineStr">
         <is>
-          <t>冰美式</t>
+          <t>热狗面包</t>
         </is>
       </c>
       <c r="AO13" s="2" t="inlineStr">
@@ -3124,12 +3124,12 @@
       </c>
       <c r="AP13" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="AQ13" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="AR13" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="AS13" s="2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>6.0</t>
         </is>
       </c>
     </row>
@@ -3166,205 +3166,659 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>W1202507251130579419</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>W1202507251130579418S</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>20230703101319100507792</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>17826157137</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>于池</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>南通分公司</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>数智化支撑中心</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-25 11:30:57</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-25 11:30:57</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>在线购物</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>咖啡测试 请勿点击</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>在线付款</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>自提</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>备货中</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-25 23:55:00</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-26 00:00:00-23:59:59</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>10270</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="inlineStr">
+        <is>
+          <t>未打印</t>
+        </is>
+      </c>
+      <c r="AF14" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG14" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH14" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI14" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ14" s="2" t="inlineStr">
+        <is>
+          <t>食堂</t>
+        </is>
+      </c>
+      <c r="AK14" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL14" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM14" s="2" t="inlineStr">
+        <is>
+          <t>125072239625</t>
+        </is>
+      </c>
+      <c r="AN14" s="2" t="inlineStr">
+        <is>
+          <t>冰美式</t>
+        </is>
+      </c>
+      <c r="AO14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AP14" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AQ14" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AR14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AS14" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>666210500150927</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>南通生产调度中心</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>118509</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>南通生产调度中心</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>W1202507251124009271</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>W1202507251124009270S</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>20230703101319100507792</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>17826157137</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>于池</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>南通分公司</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>数智化支撑中心</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-25 11:24:00</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-25 11:24:00</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>在线购物</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>咖啡测试 请勿点击</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>在线付款</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>自提</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>备货中</t>
+        </is>
+      </c>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-25 23:55:00</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-26 00:00:00-23:59:59</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>10269</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD15" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="inlineStr">
+        <is>
+          <t>未打印</t>
+        </is>
+      </c>
+      <c r="AF15" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG15" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH15" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI15" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ15" s="2" t="inlineStr">
+        <is>
+          <t>食堂</t>
+        </is>
+      </c>
+      <c r="AK15" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL15" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM15" s="2" t="inlineStr">
+        <is>
+          <t>125072239625</t>
+        </is>
+      </c>
+      <c r="AN15" s="2" t="inlineStr">
+        <is>
+          <t>冰美式</t>
+        </is>
+      </c>
+      <c r="AO15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AP15" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AQ15" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AR15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AS15" s="2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>666210500150927</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>南通生产调度中心</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>118509</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>南通生产调度中心</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>W1202507251123429261</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>W1202507251123429260S</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>20230703101319100507792</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>17826157137</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>于池</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>南通分公司</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>数智化支撑中心</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>2025-07-25 11:23:42</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>2025-07-25 11:23:42</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>在线购物</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>咖啡测试 请勿点击</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>在线付款</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>自提</t>
         </is>
       </c>
-      <c r="R14" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>备货中</t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>2025-07-25 23:55:00</t>
         </is>
       </c>
-      <c r="T14" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
         <is>
           <t>2025-07-26 00:00:00-23:59:59</t>
         </is>
       </c>
-      <c r="U14" s="2" t="inlineStr">
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>10268</t>
         </is>
       </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="X14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y14" s="2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="Z14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD14" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AE14" s="2" t="inlineStr">
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD16" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="inlineStr">
         <is>
           <t>未打印</t>
         </is>
       </c>
-      <c r="AF14" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AG14" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AH14" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AI14" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AJ14" s="2" t="inlineStr">
+      <c r="AF16" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AG16" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AH16" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AI16" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AJ16" s="2" t="inlineStr">
         <is>
           <t>食堂</t>
         </is>
       </c>
-      <c r="AK14" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AL14" s="2" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AM14" s="2" t="inlineStr">
+      <c r="AK16" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AL16" s="2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM16" s="2" t="inlineStr">
         <is>
           <t>125072239625</t>
         </is>
       </c>
-      <c r="AN14" s="2" t="inlineStr">
+      <c r="AN16" s="2" t="inlineStr">
         <is>
           <t>冰美式</t>
         </is>
       </c>
-      <c r="AO14" s="2" t="inlineStr">
+      <c r="AO16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AP14" s="2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AQ14" s="2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="AR14" s="2" t="inlineStr">
+      <c r="AP16" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AQ16" s="2" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AR16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AS14" s="2" t="inlineStr">
+      <c r="AS16" s="2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
@@ -3411,82 +3865,82 @@
     <mergeCell ref="AK1:AK2"/>
     <mergeCell ref="AL1:AL2"/>
     <mergeCell ref="AM1:AS1"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="Q7:Q8"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="S7:S8"/>
-    <mergeCell ref="T7:T8"/>
-    <mergeCell ref="U7:U8"/>
-    <mergeCell ref="V7:V8"/>
-    <mergeCell ref="W7:W8"/>
-    <mergeCell ref="X7:X8"/>
-    <mergeCell ref="Y7:Y8"/>
-    <mergeCell ref="Z7:Z8"/>
-    <mergeCell ref="AA7:AA8"/>
-    <mergeCell ref="AB7:AB8"/>
-    <mergeCell ref="AC7:AC8"/>
-    <mergeCell ref="AD7:AD8"/>
-    <mergeCell ref="AE7:AE8"/>
-    <mergeCell ref="AF7:AF8"/>
-    <mergeCell ref="AG7:AG8"/>
-    <mergeCell ref="AH7:AH8"/>
-    <mergeCell ref="AI7:AI8"/>
-    <mergeCell ref="AJ7:AJ8"/>
-    <mergeCell ref="AK7:AK8"/>
-    <mergeCell ref="AL7:AL8"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="F10:F11"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="H10:H11"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="K10:K11"/>
-    <mergeCell ref="L10:L11"/>
-    <mergeCell ref="M10:M11"/>
-    <mergeCell ref="N10:N11"/>
-    <mergeCell ref="O10:O11"/>
-    <mergeCell ref="P10:P11"/>
-    <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="R10:R11"/>
-    <mergeCell ref="S10:S11"/>
-    <mergeCell ref="T10:T11"/>
-    <mergeCell ref="U10:U11"/>
-    <mergeCell ref="V10:V11"/>
-    <mergeCell ref="W10:W11"/>
-    <mergeCell ref="X10:X11"/>
-    <mergeCell ref="Y10:Y11"/>
-    <mergeCell ref="Z10:Z11"/>
-    <mergeCell ref="AA10:AA11"/>
-    <mergeCell ref="AB10:AB11"/>
-    <mergeCell ref="AC10:AC11"/>
-    <mergeCell ref="AD10:AD11"/>
-    <mergeCell ref="AE10:AE11"/>
-    <mergeCell ref="AF10:AF11"/>
-    <mergeCell ref="AG10:AG11"/>
-    <mergeCell ref="AH10:AH11"/>
-    <mergeCell ref="AI10:AI11"/>
-    <mergeCell ref="AJ10:AJ11"/>
-    <mergeCell ref="AK10:AK11"/>
-    <mergeCell ref="AL10:AL11"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="H9:H10"/>
+    <mergeCell ref="I9:I10"/>
+    <mergeCell ref="J9:J10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="N9:N10"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="P9:P10"/>
+    <mergeCell ref="Q9:Q10"/>
+    <mergeCell ref="R9:R10"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="W9:W10"/>
+    <mergeCell ref="X9:X10"/>
+    <mergeCell ref="Y9:Y10"/>
+    <mergeCell ref="Z9:Z10"/>
+    <mergeCell ref="AA9:AA10"/>
+    <mergeCell ref="AB9:AB10"/>
+    <mergeCell ref="AC9:AC10"/>
+    <mergeCell ref="AD9:AD10"/>
+    <mergeCell ref="AE9:AE10"/>
+    <mergeCell ref="AF9:AF10"/>
+    <mergeCell ref="AG9:AG10"/>
+    <mergeCell ref="AH9:AH10"/>
+    <mergeCell ref="AI9:AI10"/>
+    <mergeCell ref="AJ9:AJ10"/>
+    <mergeCell ref="AK9:AK10"/>
+    <mergeCell ref="AL9:AL10"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="I12:I13"/>
+    <mergeCell ref="J12:J13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="M12:M13"/>
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="O12:O13"/>
+    <mergeCell ref="P12:P13"/>
+    <mergeCell ref="Q12:Q13"/>
+    <mergeCell ref="R12:R13"/>
+    <mergeCell ref="S12:S13"/>
+    <mergeCell ref="T12:T13"/>
+    <mergeCell ref="U12:U13"/>
+    <mergeCell ref="V12:V13"/>
+    <mergeCell ref="W12:W13"/>
+    <mergeCell ref="X12:X13"/>
+    <mergeCell ref="Y12:Y13"/>
+    <mergeCell ref="Z12:Z13"/>
+    <mergeCell ref="AA12:AA13"/>
+    <mergeCell ref="AB12:AB13"/>
+    <mergeCell ref="AC12:AC13"/>
+    <mergeCell ref="AD12:AD13"/>
+    <mergeCell ref="AE12:AE13"/>
+    <mergeCell ref="AF12:AF13"/>
+    <mergeCell ref="AG12:AG13"/>
+    <mergeCell ref="AH12:AH13"/>
+    <mergeCell ref="AI12:AI13"/>
+    <mergeCell ref="AJ12:AJ13"/>
+    <mergeCell ref="AK12:AK13"/>
+    <mergeCell ref="AL12:AL13"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
